--- a/docs/dms/documents/D3-SPC-01__pnl-model.xlsx
+++ b/docs/dms/documents/D3-SPC-01__pnl-model.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,35 +32,48 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Consolas"/>
-      <color rgb="006F889F"/>
       <sz val="8"/>
     </font>
     <font>
       <color rgb="006F889F"/>
       <sz val="8"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001A2B3E"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -69,22 +82,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A2B3E"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0021384F"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7DA"/>
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="006AA84F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,13 +123,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,27 +139,55 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -511,7 +562,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -539,12 +590,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MainExperts · P&amp;L · Платформа (Поток-2, самообслуживание) · ₽ · жёлтое — ввод, факт вносит основатель</t>
+          <t>MainExperts · P&amp;L · Платформа (Поток-2, самообслуживание) · ₽ · белое — ввод, серое — авто</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>июл.26</t>
@@ -737,7 +790,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
+      <c r="A5" s="12" t="inlineStr"/>
       <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Конверсия из визита в оплату</t>
@@ -748,65 +801,65 @@
           <t>маркетинг</t>
         </is>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <f>IFERROR(D7/D4,"")</f>
         <v/>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <f>IFERROR(E7/E4,"")</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <f>IFERROR(G7/G4,"")</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <f>IFERROR(H7/H4,"")</f>
         <v/>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="13">
         <f>IFERROR(J7/J4,"")</f>
         <v/>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="13">
         <f>IFERROR(K7/K4,"")</f>
         <v/>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="13">
         <f>IFERROR(M7/M4,"")</f>
         <v/>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="13">
         <f>IFERROR(N7/N4,"")</f>
         <v/>
       </c>
-      <c r="P5" s="12">
+      <c r="P5" s="13">
         <f>IFERROR(P7/P4,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="12">
+      <c r="Q5" s="13">
         <f>IFERROR(Q7/Q4,"")</f>
         <v/>
       </c>
-      <c r="S5" s="12">
+      <c r="S5" s="13">
         <f>IFERROR(S7/S4,"")</f>
         <v/>
       </c>
-      <c r="T5" s="12">
+      <c r="T5" s="13">
         <f>IFERROR(T7/T4,"")</f>
         <v/>
       </c>
-      <c r="V5" s="12">
+      <c r="V5" s="13">
         <f>IFERROR(V7/V4,"")</f>
         <v/>
       </c>
-      <c r="W5" s="12">
+      <c r="W5" s="13">
         <f>IFERROR(W7/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr"/>
+      <c r="A6" s="12" t="inlineStr"/>
       <c r="B6" s="8" t="inlineStr">
         <is>
           <t>CAC (стоимость привлечения)</t>
@@ -875,7 +928,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr"/>
+      <c r="A7" s="12" t="inlineStr"/>
       <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Кол-во оплат</t>
@@ -908,7 +961,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr"/>
       <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Средний чек</t>
@@ -977,7 +1030,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr"/>
       <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Выручка по оплатам</t>
@@ -1010,201 +1063,201 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr"/>
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Выручка всего</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>финансы</t>
         </is>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="17">
         <f>IFERROR(D9,"")</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="17">
         <f>IFERROR(E9,"")</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="18">
         <f>IFERROR(E10/E10,"")</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="17">
         <f>IFERROR(G9,"")</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="17">
         <f>IFERROR(H9,"")</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="18">
         <f>IFERROR(H10/H10,"")</f>
         <v/>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="17">
         <f>IFERROR(J9,"")</f>
         <v/>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="17">
         <f>IFERROR(K9,"")</f>
         <v/>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="18">
         <f>IFERROR(K10/K10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="17">
         <f>IFERROR(M9,"")</f>
         <v/>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="17">
         <f>IFERROR(N9,"")</f>
         <v/>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="18">
         <f>IFERROR(N10/N10,"")</f>
         <v/>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="17">
         <f>IFERROR(P9,"")</f>
         <v/>
       </c>
-      <c r="Q10" s="11">
+      <c r="Q10" s="17">
         <f>IFERROR(Q9,"")</f>
         <v/>
       </c>
-      <c r="R10" s="12">
+      <c r="R10" s="18">
         <f>IFERROR(Q10/Q10,"")</f>
         <v/>
       </c>
-      <c r="S10" s="11">
+      <c r="S10" s="17">
         <f>IFERROR(S9,"")</f>
         <v/>
       </c>
-      <c r="T10" s="11">
+      <c r="T10" s="17">
         <f>IFERROR(T9,"")</f>
         <v/>
       </c>
-      <c r="U10" s="12">
+      <c r="U10" s="18">
         <f>IFERROR(T10/T10,"")</f>
         <v/>
       </c>
-      <c r="V10" s="14">
+      <c r="V10" s="19">
         <f>IFERROR(V9,"")</f>
         <v/>
       </c>
-      <c r="W10" s="14">
+      <c r="W10" s="19">
         <f>IFERROR(W9,"")</f>
         <v/>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="18">
         <f>IFERROR(W10/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr"/>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Расходы всего</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>финансы</t>
         </is>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="23">
         <f>IFERROR(SUM(D12:D18),"")</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="23">
         <f>IFERROR(SUM(E12:E18),"")</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="24">
         <f>IFERROR(E11/E10,"")</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="23">
         <f>IFERROR(SUM(G12:G18),"")</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="23">
         <f>IFERROR(SUM(H12:H18),"")</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="24">
         <f>IFERROR(H11/H10,"")</f>
         <v/>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="23">
         <f>IFERROR(SUM(J12:J18),"")</f>
         <v/>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="23">
         <f>IFERROR(SUM(K12:K18),"")</f>
         <v/>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="24">
         <f>IFERROR(K11/K10,"")</f>
         <v/>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="23">
         <f>IFERROR(SUM(M12:M18),"")</f>
         <v/>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="23">
         <f>IFERROR(SUM(N12:N18),"")</f>
         <v/>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="24">
         <f>IFERROR(N11/N10,"")</f>
         <v/>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="23">
         <f>IFERROR(SUM(P12:P18),"")</f>
         <v/>
       </c>
-      <c r="Q11" s="11">
+      <c r="Q11" s="23">
         <f>IFERROR(SUM(Q12:Q18),"")</f>
         <v/>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="24">
         <f>IFERROR(Q11/Q10,"")</f>
         <v/>
       </c>
-      <c r="S11" s="11">
+      <c r="S11" s="23">
         <f>IFERROR(SUM(S12:S18),"")</f>
         <v/>
       </c>
-      <c r="T11" s="11">
+      <c r="T11" s="23">
         <f>IFERROR(SUM(T12:T18),"")</f>
         <v/>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="24">
         <f>IFERROR(T11/T10,"")</f>
         <v/>
       </c>
-      <c r="V11" s="14">
+      <c r="V11" s="25">
         <f>IFERROR(SUM(V12:V18),"")</f>
         <v/>
       </c>
-      <c r="W11" s="14">
+      <c r="W11" s="25">
         <f>IFERROR(SUM(W12:W18),"")</f>
         <v/>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="26">
         <f>IFERROR(W11/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -1221,37 +1274,37 @@
       </c>
       <c r="D12" s="10" t="n"/>
       <c r="E12" s="10" t="n"/>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>IFERROR(E12/E10,"")</f>
         <v/>
       </c>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n"/>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <f>IFERROR(H12/H10,"")</f>
         <v/>
       </c>
       <c r="J12" s="10" t="n"/>
       <c r="K12" s="10" t="n"/>
-      <c r="L12" s="12">
+      <c r="L12" s="13">
         <f>IFERROR(K12/K10,"")</f>
         <v/>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="10" t="n"/>
-      <c r="O12" s="12">
+      <c r="O12" s="13">
         <f>IFERROR(N12/N10,"")</f>
         <v/>
       </c>
       <c r="P12" s="10" t="n"/>
       <c r="Q12" s="10" t="n"/>
-      <c r="R12" s="12">
+      <c r="R12" s="13">
         <f>IFERROR(Q12/Q10,"")</f>
         <v/>
       </c>
       <c r="S12" s="10" t="n"/>
       <c r="T12" s="10" t="n"/>
-      <c r="U12" s="12">
+      <c r="U12" s="13">
         <f>IFERROR(T12/T10,"")</f>
         <v/>
       </c>
@@ -1263,60 +1316,60 @@
         <f>IFERROR(E12+H12+K12+N12+Q12+T12,"")</f>
         <v/>
       </c>
-      <c r="X12" s="12">
+      <c r="X12" s="13">
         <f>IFERROR(W12/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>ФОТ Маркетинг (вкл. операторов)</t>
+          <t>ФОТ Платформа (разработка, маркетинг, владелец, Саша, Вадим)</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>маркетинг</t>
+          <t>операционка</t>
         </is>
       </c>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>IFERROR(E13/E10,"")</f>
         <v/>
       </c>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <f>IFERROR(H13/H10,"")</f>
         <v/>
       </c>
       <c r="J13" s="10" t="n"/>
       <c r="K13" s="10" t="n"/>
-      <c r="L13" s="12">
+      <c r="L13" s="13">
         <f>IFERROR(K13/K10,"")</f>
         <v/>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="10" t="n"/>
-      <c r="O13" s="12">
+      <c r="O13" s="13">
         <f>IFERROR(N13/N10,"")</f>
         <v/>
       </c>
       <c r="P13" s="10" t="n"/>
       <c r="Q13" s="10" t="n"/>
-      <c r="R13" s="12">
+      <c r="R13" s="13">
         <f>IFERROR(Q13/Q10,"")</f>
         <v/>
       </c>
       <c r="S13" s="10" t="n"/>
       <c r="T13" s="10" t="n"/>
-      <c r="U13" s="12">
+      <c r="U13" s="13">
         <f>IFERROR(T13/T10,"")</f>
         <v/>
       </c>
@@ -1328,13 +1381,13 @@
         <f>IFERROR(E13+H13+K13+N13+Q13+T13,"")</f>
         <v/>
       </c>
-      <c r="X13" s="12">
+      <c r="X13" s="13">
         <f>IFERROR(W13/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -1351,37 +1404,37 @@
       </c>
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="10" t="n"/>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>IFERROR(E14/E10,"")</f>
         <v/>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n"/>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <f>IFERROR(H14/H10,"")</f>
         <v/>
       </c>
       <c r="J14" s="10" t="n"/>
       <c r="K14" s="10" t="n"/>
-      <c r="L14" s="12">
+      <c r="L14" s="13">
         <f>IFERROR(K14/K10,"")</f>
         <v/>
       </c>
       <c r="M14" s="10" t="n"/>
       <c r="N14" s="10" t="n"/>
-      <c r="O14" s="12">
+      <c r="O14" s="13">
         <f>IFERROR(N14/N10,"")</f>
         <v/>
       </c>
       <c r="P14" s="10" t="n"/>
       <c r="Q14" s="10" t="n"/>
-      <c r="R14" s="12">
+      <c r="R14" s="13">
         <f>IFERROR(Q14/Q10,"")</f>
         <v/>
       </c>
       <c r="S14" s="10" t="n"/>
       <c r="T14" s="10" t="n"/>
-      <c r="U14" s="12">
+      <c r="U14" s="13">
         <f>IFERROR(T14/T10,"")</f>
         <v/>
       </c>
@@ -1393,13 +1446,13 @@
         <f>IFERROR(E14+H14+K14+N14+Q14+T14,"")</f>
         <v/>
       </c>
-      <c r="X14" s="12">
+      <c r="X14" s="13">
         <f>IFERROR(W14/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Pr</t>
         </is>
@@ -1416,37 +1469,37 @@
       </c>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>IFERROR(E15/E10,"")</f>
         <v/>
       </c>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n"/>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <f>IFERROR(H15/H10,"")</f>
         <v/>
       </c>
       <c r="J15" s="10" t="n"/>
       <c r="K15" s="10" t="n"/>
-      <c r="L15" s="12">
+      <c r="L15" s="13">
         <f>IFERROR(K15/K10,"")</f>
         <v/>
       </c>
       <c r="M15" s="10" t="n"/>
       <c r="N15" s="10" t="n"/>
-      <c r="O15" s="12">
+      <c r="O15" s="13">
         <f>IFERROR(N15/N10,"")</f>
         <v/>
       </c>
       <c r="P15" s="10" t="n"/>
       <c r="Q15" s="10" t="n"/>
-      <c r="R15" s="12">
+      <c r="R15" s="13">
         <f>IFERROR(Q15/Q10,"")</f>
         <v/>
       </c>
       <c r="S15" s="10" t="n"/>
       <c r="T15" s="10" t="n"/>
-      <c r="U15" s="12">
+      <c r="U15" s="13">
         <f>IFERROR(T15/T10,"")</f>
         <v/>
       </c>
@@ -1458,13 +1511,13 @@
         <f>IFERROR(E15+H15+K15+N15+Q15+T15,"")</f>
         <v/>
       </c>
-      <c r="X15" s="12">
+      <c r="X15" s="13">
         <f>IFERROR(W15/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Pr</t>
         </is>
@@ -1481,37 +1534,37 @@
       </c>
       <c r="D16" s="10" t="n"/>
       <c r="E16" s="10" t="n"/>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>IFERROR(E16/E10,"")</f>
         <v/>
       </c>
       <c r="G16" s="10" t="n"/>
       <c r="H16" s="10" t="n"/>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <f>IFERROR(H16/H10,"")</f>
         <v/>
       </c>
       <c r="J16" s="10" t="n"/>
       <c r="K16" s="10" t="n"/>
-      <c r="L16" s="12">
+      <c r="L16" s="13">
         <f>IFERROR(K16/K10,"")</f>
         <v/>
       </c>
       <c r="M16" s="10" t="n"/>
       <c r="N16" s="10" t="n"/>
-      <c r="O16" s="12">
+      <c r="O16" s="13">
         <f>IFERROR(N16/N10,"")</f>
         <v/>
       </c>
       <c r="P16" s="10" t="n"/>
       <c r="Q16" s="10" t="n"/>
-      <c r="R16" s="12">
+      <c r="R16" s="13">
         <f>IFERROR(Q16/Q10,"")</f>
         <v/>
       </c>
       <c r="S16" s="10" t="n"/>
       <c r="T16" s="10" t="n"/>
-      <c r="U16" s="12">
+      <c r="U16" s="13">
         <f>IFERROR(T16/T10,"")</f>
         <v/>
       </c>
@@ -1523,13 +1576,13 @@
         <f>IFERROR(E16+H16+K16+N16+Q16+T16,"")</f>
         <v/>
       </c>
-      <c r="X16" s="12">
+      <c r="X16" s="13">
         <f>IFERROR(W16/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1552,7 +1605,7 @@
         <f>IFERROR(E10*0.1,"")</f>
         <v/>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <f>IFERROR(E17/E10,"")</f>
         <v/>
       </c>
@@ -1564,7 +1617,7 @@
         <f>IFERROR(H10*0.1,"")</f>
         <v/>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <f>IFERROR(H17/H10,"")</f>
         <v/>
       </c>
@@ -1576,7 +1629,7 @@
         <f>IFERROR(K10*0.1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="13">
         <f>IFERROR(K17/K10,"")</f>
         <v/>
       </c>
@@ -1588,7 +1641,7 @@
         <f>IFERROR(N10*0.1,"")</f>
         <v/>
       </c>
-      <c r="O17" s="12">
+      <c r="O17" s="13">
         <f>IFERROR(N17/N10,"")</f>
         <v/>
       </c>
@@ -1600,7 +1653,7 @@
         <f>IFERROR(Q10*0.1,"")</f>
         <v/>
       </c>
-      <c r="R17" s="12">
+      <c r="R17" s="13">
         <f>IFERROR(Q17/Q10,"")</f>
         <v/>
       </c>
@@ -1612,7 +1665,7 @@
         <f>IFERROR(T10*0.1,"")</f>
         <v/>
       </c>
-      <c r="U17" s="12">
+      <c r="U17" s="13">
         <f>IFERROR(T17/T10,"")</f>
         <v/>
       </c>
@@ -1624,13 +1677,13 @@
         <f>IFERROR(W10*0.1,"")</f>
         <v/>
       </c>
-      <c r="X17" s="12">
+      <c r="X17" s="13">
         <f>IFERROR(W17/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1647,37 +1700,37 @@
       </c>
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <f>IFERROR(E18/E10,"")</f>
         <v/>
       </c>
       <c r="G18" s="10" t="n"/>
       <c r="H18" s="10" t="n"/>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <f>IFERROR(H18/H10,"")</f>
         <v/>
       </c>
       <c r="J18" s="10" t="n"/>
       <c r="K18" s="10" t="n"/>
-      <c r="L18" s="12">
+      <c r="L18" s="13">
         <f>IFERROR(K18/K10,"")</f>
         <v/>
       </c>
       <c r="M18" s="10" t="n"/>
       <c r="N18" s="10" t="n"/>
-      <c r="O18" s="12">
+      <c r="O18" s="13">
         <f>IFERROR(N18/N10,"")</f>
         <v/>
       </c>
       <c r="P18" s="10" t="n"/>
       <c r="Q18" s="10" t="n"/>
-      <c r="R18" s="12">
+      <c r="R18" s="13">
         <f>IFERROR(Q18/Q10,"")</f>
         <v/>
       </c>
       <c r="S18" s="10" t="n"/>
       <c r="T18" s="10" t="n"/>
-      <c r="U18" s="12">
+      <c r="U18" s="13">
         <f>IFERROR(T18/T10,"")</f>
         <v/>
       </c>
@@ -1689,110 +1742,110 @@
         <f>IFERROR(E18+H18+K18+N18+Q18+T18,"")</f>
         <v/>
       </c>
-      <c r="X18" s="12">
+      <c r="X18" s="13">
         <f>IFERROR(W18/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr"/>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr"/>
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Маржинальная прибыль</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>финансы</t>
         </is>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="17">
         <f>IFERROR(D10-D11,"")</f>
         <v/>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="17">
         <f>IFERROR(E10-E11,"")</f>
         <v/>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="18">
         <f>IFERROR(E19/E10,"")</f>
         <v/>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="17">
         <f>IFERROR(G10-G11,"")</f>
         <v/>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="17">
         <f>IFERROR(H10-H11,"")</f>
         <v/>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="18">
         <f>IFERROR(H19/H10,"")</f>
         <v/>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="17">
         <f>IFERROR(J10-J11,"")</f>
         <v/>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="17">
         <f>IFERROR(K10-K11,"")</f>
         <v/>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="18">
         <f>IFERROR(K19/K10,"")</f>
         <v/>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="17">
         <f>IFERROR(M10-M11,"")</f>
         <v/>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="17">
         <f>IFERROR(N10-N11,"")</f>
         <v/>
       </c>
-      <c r="O19" s="12">
+      <c r="O19" s="18">
         <f>IFERROR(N19/N10,"")</f>
         <v/>
       </c>
-      <c r="P19" s="11">
+      <c r="P19" s="17">
         <f>IFERROR(P10-P11,"")</f>
         <v/>
       </c>
-      <c r="Q19" s="11">
+      <c r="Q19" s="17">
         <f>IFERROR(Q10-Q11,"")</f>
         <v/>
       </c>
-      <c r="R19" s="12">
+      <c r="R19" s="18">
         <f>IFERROR(Q19/Q10,"")</f>
         <v/>
       </c>
-      <c r="S19" s="11">
+      <c r="S19" s="17">
         <f>IFERROR(S10-S11,"")</f>
         <v/>
       </c>
-      <c r="T19" s="11">
+      <c r="T19" s="17">
         <f>IFERROR(T10-T11,"")</f>
         <v/>
       </c>
-      <c r="U19" s="12">
+      <c r="U19" s="18">
         <f>IFERROR(T19/T10,"")</f>
         <v/>
       </c>
-      <c r="V19" s="14">
+      <c r="V19" s="19">
         <f>IFERROR(V10-V11,"")</f>
         <v/>
       </c>
-      <c r="W19" s="14">
+      <c r="W19" s="19">
         <f>IFERROR(W10-W11,"")</f>
         <v/>
       </c>
-      <c r="X19" s="12">
+      <c r="X19" s="18">
         <f>IFERROR(W19/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr"/>
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Выручка с 1 оплаты</t>
@@ -1861,7 +1914,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr"/>
       <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Расходы на 1 оплату</t>
@@ -1930,7 +1983,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr"/>
       <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Маржинальная прибыль на 1 оплату</t>
@@ -1999,7 +2052,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr"/>
+      <c r="A23" s="12" t="inlineStr"/>
       <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Маржинальность оплаты</t>
@@ -2010,59 +2063,59 @@
           <t>финансы</t>
         </is>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="13">
         <f>IFERROR((D20-D21)/D20,"")</f>
         <v/>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="13">
         <f>IFERROR((E20-E21)/E20,"")</f>
         <v/>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="13">
         <f>IFERROR((G20-G21)/G20,"")</f>
         <v/>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="13">
         <f>IFERROR((H20-H21)/H20,"")</f>
         <v/>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="13">
         <f>IFERROR((J20-J21)/J20,"")</f>
         <v/>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="13">
         <f>IFERROR((K20-K21)/K20,"")</f>
         <v/>
       </c>
-      <c r="M23" s="12">
+      <c r="M23" s="13">
         <f>IFERROR((M20-M21)/M20,"")</f>
         <v/>
       </c>
-      <c r="N23" s="12">
+      <c r="N23" s="13">
         <f>IFERROR((N20-N21)/N20,"")</f>
         <v/>
       </c>
-      <c r="P23" s="12">
+      <c r="P23" s="13">
         <f>IFERROR((P20-P21)/P20,"")</f>
         <v/>
       </c>
-      <c r="Q23" s="12">
+      <c r="Q23" s="13">
         <f>IFERROR((Q20-Q21)/Q20,"")</f>
         <v/>
       </c>
-      <c r="S23" s="12">
+      <c r="S23" s="13">
         <f>IFERROR((S20-S21)/S20,"")</f>
         <v/>
       </c>
-      <c r="T23" s="12">
+      <c r="T23" s="13">
         <f>IFERROR((T20-T21)/T20,"")</f>
         <v/>
       </c>
-      <c r="V23" s="12">
+      <c r="V23" s="13">
         <f>IFERROR((V20-V21)/V20,"")</f>
         <v/>
       </c>
-      <c r="W23" s="12">
+      <c r="W23" s="13">
         <f>IFERROR((W20-W21)/W20,"")</f>
         <v/>
       </c>
@@ -2092,7 +2145,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2120,12 +2173,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MainExperts · P&amp;L · Поток-1 (агентство / личные продажи, 2 менеджера) · ₽ · жёлтое — ввод</t>
+          <t>MainExperts · P&amp;L · Поток-1 (агентство / личные продажи, 2 менеджера) · ₽ · белое — ввод, серое — авто</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>июл.26</t>
@@ -2285,7 +2340,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr"/>
+      <c r="A4" s="28" t="inlineStr"/>
       <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Кол-во входящих лидов</t>
@@ -2318,7 +2373,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
+      <c r="A5" s="12" t="inlineStr"/>
       <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Кол-во созвонов</t>
@@ -2351,7 +2406,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr"/>
+      <c r="A6" s="12" t="inlineStr"/>
       <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Конверсия лид→созвон</t>
@@ -2362,65 +2417,65 @@
           <t>продажи</t>
         </is>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="13">
         <f>IFERROR(D5/D4,"")</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <f>IFERROR(E5/E4,"")</f>
         <v/>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="13">
         <f>IFERROR(G5/G4,"")</f>
         <v/>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="13">
         <f>IFERROR(H5/H4,"")</f>
         <v/>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="13">
         <f>IFERROR(J5/J4,"")</f>
         <v/>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="13">
         <f>IFERROR(K5/K4,"")</f>
         <v/>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="13">
         <f>IFERROR(M5/M4,"")</f>
         <v/>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="13">
         <f>IFERROR(N5/N4,"")</f>
         <v/>
       </c>
-      <c r="P6" s="12">
+      <c r="P6" s="13">
         <f>IFERROR(P5/P4,"")</f>
         <v/>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="13">
         <f>IFERROR(Q5/Q4,"")</f>
         <v/>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="13">
         <f>IFERROR(S5/S4,"")</f>
         <v/>
       </c>
-      <c r="T6" s="12">
+      <c r="T6" s="13">
         <f>IFERROR(T5/T4,"")</f>
         <v/>
       </c>
-      <c r="V6" s="12">
+      <c r="V6" s="13">
         <f>IFERROR(V5/V4,"")</f>
         <v/>
       </c>
-      <c r="W6" s="12">
+      <c r="W6" s="13">
         <f>IFERROR(W5/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr"/>
+      <c r="A7" s="12" t="inlineStr"/>
       <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Кол-во оплат</t>
@@ -2453,7 +2508,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr"/>
       <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Конверсия созвон→оплата</t>
@@ -2464,65 +2519,65 @@
           <t>продажи</t>
         </is>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>IFERROR(D7/D5,"")</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>IFERROR(E7/E5,"")</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>IFERROR(G7/G5,"")</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <f>IFERROR(H7/H5,"")</f>
         <v/>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="13">
         <f>IFERROR(J7/J5,"")</f>
         <v/>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="13">
         <f>IFERROR(K7/K5,"")</f>
         <v/>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="13">
         <f>IFERROR(M7/M5,"")</f>
         <v/>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="13">
         <f>IFERROR(N7/N5,"")</f>
         <v/>
       </c>
-      <c r="P8" s="12">
+      <c r="P8" s="13">
         <f>IFERROR(P7/P5,"")</f>
         <v/>
       </c>
-      <c r="Q8" s="12">
+      <c r="Q8" s="13">
         <f>IFERROR(Q7/Q5,"")</f>
         <v/>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="13">
         <f>IFERROR(S7/S5,"")</f>
         <v/>
       </c>
-      <c r="T8" s="12">
+      <c r="T8" s="13">
         <f>IFERROR(T7/T5,"")</f>
         <v/>
       </c>
-      <c r="V8" s="12">
+      <c r="V8" s="13">
         <f>IFERROR(V7/V5,"")</f>
         <v/>
       </c>
-      <c r="W8" s="12">
+      <c r="W8" s="13">
         <f>IFERROR(W7/W5,"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr"/>
       <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Средний чек</t>
@@ -2591,165 +2646,165 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr"/>
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Сумма оплат (выручка)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>финансы</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="12">
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="18">
         <f>IFERROR(E10/E10,"")</f>
         <v/>
       </c>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="12">
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="18">
         <f>IFERROR(H10/H10,"")</f>
         <v/>
       </c>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="12">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="18">
         <f>IFERROR(K10/K10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="12">
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="17" t="n"/>
+      <c r="O10" s="18">
         <f>IFERROR(N10/N10,"")</f>
         <v/>
       </c>
-      <c r="P10" s="10" t="n"/>
-      <c r="Q10" s="10" t="n"/>
-      <c r="R10" s="12">
+      <c r="P10" s="17" t="n"/>
+      <c r="Q10" s="17" t="n"/>
+      <c r="R10" s="18">
         <f>IFERROR(Q10/Q10,"")</f>
         <v/>
       </c>
-      <c r="S10" s="10" t="n"/>
-      <c r="T10" s="10" t="n"/>
-      <c r="U10" s="12">
+      <c r="S10" s="17" t="n"/>
+      <c r="T10" s="17" t="n"/>
+      <c r="U10" s="18">
         <f>IFERROR(T10/T10,"")</f>
         <v/>
       </c>
-      <c r="V10" s="14">
+      <c r="V10" s="19">
         <f>IFERROR(D10+G10+J10+M10+P10+S10,"")</f>
         <v/>
       </c>
-      <c r="W10" s="14">
+      <c r="W10" s="19">
         <f>IFERROR(E10+H10+K10+N10+Q10+T10,"")</f>
         <v/>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="18">
         <f>IFERROR(W10/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr"/>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Расходы всего</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>финансы</t>
         </is>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="23">
         <f>IFERROR(SUM(D12:D17),"")</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="23">
         <f>IFERROR(SUM(E12:E17),"")</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="24">
         <f>IFERROR(E11/E10,"")</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="23">
         <f>IFERROR(SUM(G12:G17),"")</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="23">
         <f>IFERROR(SUM(H12:H17),"")</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="24">
         <f>IFERROR(H11/H10,"")</f>
         <v/>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="23">
         <f>IFERROR(SUM(J12:J17),"")</f>
         <v/>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="23">
         <f>IFERROR(SUM(K12:K17),"")</f>
         <v/>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="24">
         <f>IFERROR(K11/K10,"")</f>
         <v/>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="23">
         <f>IFERROR(SUM(M12:M17),"")</f>
         <v/>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="23">
         <f>IFERROR(SUM(N12:N17),"")</f>
         <v/>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="24">
         <f>IFERROR(N11/N10,"")</f>
         <v/>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="23">
         <f>IFERROR(SUM(P12:P17),"")</f>
         <v/>
       </c>
-      <c r="Q11" s="11">
+      <c r="Q11" s="23">
         <f>IFERROR(SUM(Q12:Q17),"")</f>
         <v/>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="24">
         <f>IFERROR(Q11/Q10,"")</f>
         <v/>
       </c>
-      <c r="S11" s="11">
+      <c r="S11" s="23">
         <f>IFERROR(SUM(S12:S17),"")</f>
         <v/>
       </c>
-      <c r="T11" s="11">
+      <c r="T11" s="23">
         <f>IFERROR(SUM(T12:T17),"")</f>
         <v/>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="24">
         <f>IFERROR(T11/T10,"")</f>
         <v/>
       </c>
-      <c r="V11" s="14">
+      <c r="V11" s="25">
         <f>IFERROR(SUM(V12:V17),"")</f>
         <v/>
       </c>
-      <c r="W11" s="14">
+      <c r="W11" s="25">
         <f>IFERROR(SUM(W12:W17),"")</f>
         <v/>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="26">
         <f>IFERROR(W11/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -2766,37 +2821,37 @@
       </c>
       <c r="D12" s="10" t="n"/>
       <c r="E12" s="10" t="n"/>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>IFERROR(E12/E10,"")</f>
         <v/>
       </c>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n"/>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <f>IFERROR(H12/H10,"")</f>
         <v/>
       </c>
       <c r="J12" s="10" t="n"/>
       <c r="K12" s="10" t="n"/>
-      <c r="L12" s="12">
+      <c r="L12" s="13">
         <f>IFERROR(K12/K10,"")</f>
         <v/>
       </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="10" t="n"/>
-      <c r="O12" s="12">
+      <c r="O12" s="13">
         <f>IFERROR(N12/N10,"")</f>
         <v/>
       </c>
       <c r="P12" s="10" t="n"/>
       <c r="Q12" s="10" t="n"/>
-      <c r="R12" s="12">
+      <c r="R12" s="13">
         <f>IFERROR(Q12/Q10,"")</f>
         <v/>
       </c>
       <c r="S12" s="10" t="n"/>
       <c r="T12" s="10" t="n"/>
-      <c r="U12" s="12">
+      <c r="U12" s="13">
         <f>IFERROR(T12/T10,"")</f>
         <v/>
       </c>
@@ -2808,13 +2863,13 @@
         <f>IFERROR(E12+H12+K12+N12+Q12+T12,"")</f>
         <v/>
       </c>
-      <c r="X12" s="12">
+      <c r="X12" s="13">
         <f>IFERROR(W12/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -2831,37 +2886,37 @@
       </c>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>IFERROR(E13/E10,"")</f>
         <v/>
       </c>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <f>IFERROR(H13/H10,"")</f>
         <v/>
       </c>
       <c r="J13" s="10" t="n"/>
       <c r="K13" s="10" t="n"/>
-      <c r="L13" s="12">
+      <c r="L13" s="13">
         <f>IFERROR(K13/K10,"")</f>
         <v/>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="10" t="n"/>
-      <c r="O13" s="12">
+      <c r="O13" s="13">
         <f>IFERROR(N13/N10,"")</f>
         <v/>
       </c>
       <c r="P13" s="10" t="n"/>
       <c r="Q13" s="10" t="n"/>
-      <c r="R13" s="12">
+      <c r="R13" s="13">
         <f>IFERROR(Q13/Q10,"")</f>
         <v/>
       </c>
       <c r="S13" s="10" t="n"/>
       <c r="T13" s="10" t="n"/>
-      <c r="U13" s="12">
+      <c r="U13" s="13">
         <f>IFERROR(T13/T10,"")</f>
         <v/>
       </c>
@@ -2873,13 +2928,13 @@
         <f>IFERROR(E13+H13+K13+N13+Q13+T13,"")</f>
         <v/>
       </c>
-      <c r="X13" s="12">
+      <c r="X13" s="13">
         <f>IFERROR(W13/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -2896,37 +2951,37 @@
       </c>
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="10" t="n"/>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>IFERROR(E14/E10,"")</f>
         <v/>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n"/>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <f>IFERROR(H14/H10,"")</f>
         <v/>
       </c>
       <c r="J14" s="10" t="n"/>
       <c r="K14" s="10" t="n"/>
-      <c r="L14" s="12">
+      <c r="L14" s="13">
         <f>IFERROR(K14/K10,"")</f>
         <v/>
       </c>
       <c r="M14" s="10" t="n"/>
       <c r="N14" s="10" t="n"/>
-      <c r="O14" s="12">
+      <c r="O14" s="13">
         <f>IFERROR(N14/N10,"")</f>
         <v/>
       </c>
       <c r="P14" s="10" t="n"/>
       <c r="Q14" s="10" t="n"/>
-      <c r="R14" s="12">
+      <c r="R14" s="13">
         <f>IFERROR(Q14/Q10,"")</f>
         <v/>
       </c>
       <c r="S14" s="10" t="n"/>
       <c r="T14" s="10" t="n"/>
-      <c r="U14" s="12">
+      <c r="U14" s="13">
         <f>IFERROR(T14/T10,"")</f>
         <v/>
       </c>
@@ -2938,13 +2993,13 @@
         <f>IFERROR(E14+H14+K14+N14+Q14+T14,"")</f>
         <v/>
       </c>
-      <c r="X14" s="12">
+      <c r="X14" s="13">
         <f>IFERROR(W14/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -2961,37 +3016,37 @@
       </c>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>IFERROR(E15/E10,"")</f>
         <v/>
       </c>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n"/>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <f>IFERROR(H15/H10,"")</f>
         <v/>
       </c>
       <c r="J15" s="10" t="n"/>
       <c r="K15" s="10" t="n"/>
-      <c r="L15" s="12">
+      <c r="L15" s="13">
         <f>IFERROR(K15/K10,"")</f>
         <v/>
       </c>
       <c r="M15" s="10" t="n"/>
       <c r="N15" s="10" t="n"/>
-      <c r="O15" s="12">
+      <c r="O15" s="13">
         <f>IFERROR(N15/N10,"")</f>
         <v/>
       </c>
       <c r="P15" s="10" t="n"/>
       <c r="Q15" s="10" t="n"/>
-      <c r="R15" s="12">
+      <c r="R15" s="13">
         <f>IFERROR(Q15/Q10,"")</f>
         <v/>
       </c>
       <c r="S15" s="10" t="n"/>
       <c r="T15" s="10" t="n"/>
-      <c r="U15" s="12">
+      <c r="U15" s="13">
         <f>IFERROR(T15/T10,"")</f>
         <v/>
       </c>
@@ -3003,13 +3058,13 @@
         <f>IFERROR(E15+H15+K15+N15+Q15+T15,"")</f>
         <v/>
       </c>
-      <c r="X15" s="12">
+      <c r="X15" s="13">
         <f>IFERROR(W15/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3032,7 +3087,7 @@
         <f>IFERROR(E10*0.1,"")</f>
         <v/>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>IFERROR(E16/E10,"")</f>
         <v/>
       </c>
@@ -3044,7 +3099,7 @@
         <f>IFERROR(H10*0.1,"")</f>
         <v/>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <f>IFERROR(H16/H10,"")</f>
         <v/>
       </c>
@@ -3056,7 +3111,7 @@
         <f>IFERROR(K10*0.1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="13">
         <f>IFERROR(K16/K10,"")</f>
         <v/>
       </c>
@@ -3068,7 +3123,7 @@
         <f>IFERROR(N10*0.1,"")</f>
         <v/>
       </c>
-      <c r="O16" s="12">
+      <c r="O16" s="13">
         <f>IFERROR(N16/N10,"")</f>
         <v/>
       </c>
@@ -3080,7 +3135,7 @@
         <f>IFERROR(Q10*0.1,"")</f>
         <v/>
       </c>
-      <c r="R16" s="12">
+      <c r="R16" s="13">
         <f>IFERROR(Q16/Q10,"")</f>
         <v/>
       </c>
@@ -3092,7 +3147,7 @@
         <f>IFERROR(T10*0.1,"")</f>
         <v/>
       </c>
-      <c r="U16" s="12">
+      <c r="U16" s="13">
         <f>IFERROR(T16/T10,"")</f>
         <v/>
       </c>
@@ -3104,13 +3159,13 @@
         <f>IFERROR(W10*0.1,"")</f>
         <v/>
       </c>
-      <c r="X16" s="12">
+      <c r="X16" s="13">
         <f>IFERROR(W16/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3127,37 +3182,37 @@
       </c>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <f>IFERROR(E17/E10,"")</f>
         <v/>
       </c>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n"/>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <f>IFERROR(H17/H10,"")</f>
         <v/>
       </c>
       <c r="J17" s="10" t="n"/>
       <c r="K17" s="10" t="n"/>
-      <c r="L17" s="12">
+      <c r="L17" s="13">
         <f>IFERROR(K17/K10,"")</f>
         <v/>
       </c>
       <c r="M17" s="10" t="n"/>
       <c r="N17" s="10" t="n"/>
-      <c r="O17" s="12">
+      <c r="O17" s="13">
         <f>IFERROR(N17/N10,"")</f>
         <v/>
       </c>
       <c r="P17" s="10" t="n"/>
       <c r="Q17" s="10" t="n"/>
-      <c r="R17" s="12">
+      <c r="R17" s="13">
         <f>IFERROR(Q17/Q10,"")</f>
         <v/>
       </c>
       <c r="S17" s="10" t="n"/>
       <c r="T17" s="10" t="n"/>
-      <c r="U17" s="12">
+      <c r="U17" s="13">
         <f>IFERROR(T17/T10,"")</f>
         <v/>
       </c>
@@ -3169,110 +3224,110 @@
         <f>IFERROR(E17+H17+K17+N17+Q17+T17,"")</f>
         <v/>
       </c>
-      <c r="X17" s="12">
+      <c r="X17" s="13">
         <f>IFERROR(W17/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr"/>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr"/>
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Маржинальная прибыль</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>финансы</t>
         </is>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="17">
         <f>IFERROR(D10-D11,"")</f>
         <v/>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="17">
         <f>IFERROR(E10-E11,"")</f>
         <v/>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="18">
         <f>IFERROR(E18/E10,"")</f>
         <v/>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="17">
         <f>IFERROR(G10-G11,"")</f>
         <v/>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="17">
         <f>IFERROR(H10-H11,"")</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="18">
         <f>IFERROR(H18/H10,"")</f>
         <v/>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="17">
         <f>IFERROR(J10-J11,"")</f>
         <v/>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="17">
         <f>IFERROR(K10-K11,"")</f>
         <v/>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="18">
         <f>IFERROR(K18/K10,"")</f>
         <v/>
       </c>
-      <c r="M18" s="11">
+      <c r="M18" s="17">
         <f>IFERROR(M10-M11,"")</f>
         <v/>
       </c>
-      <c r="N18" s="11">
+      <c r="N18" s="17">
         <f>IFERROR(N10-N11,"")</f>
         <v/>
       </c>
-      <c r="O18" s="12">
+      <c r="O18" s="18">
         <f>IFERROR(N18/N10,"")</f>
         <v/>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="17">
         <f>IFERROR(P10-P11,"")</f>
         <v/>
       </c>
-      <c r="Q18" s="11">
+      <c r="Q18" s="17">
         <f>IFERROR(Q10-Q11,"")</f>
         <v/>
       </c>
-      <c r="R18" s="12">
+      <c r="R18" s="18">
         <f>IFERROR(Q18/Q10,"")</f>
         <v/>
       </c>
-      <c r="S18" s="11">
+      <c r="S18" s="17">
         <f>IFERROR(S10-S11,"")</f>
         <v/>
       </c>
-      <c r="T18" s="11">
+      <c r="T18" s="17">
         <f>IFERROR(T10-T11,"")</f>
         <v/>
       </c>
-      <c r="U18" s="12">
+      <c r="U18" s="18">
         <f>IFERROR(T18/T10,"")</f>
         <v/>
       </c>
-      <c r="V18" s="14">
+      <c r="V18" s="19">
         <f>IFERROR(V10-V11,"")</f>
         <v/>
       </c>
-      <c r="W18" s="14">
+      <c r="W18" s="19">
         <f>IFERROR(W10-W11,"")</f>
         <v/>
       </c>
-      <c r="X18" s="12">
+      <c r="X18" s="18">
         <f>IFERROR(W18/W10,"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr"/>
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Выручка с 1 оплаты</t>
@@ -3341,7 +3396,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr"/>
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Расходы на 1 оплату</t>
@@ -3410,7 +3465,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr"/>
       <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Маржинальная прибыль на 1 оплату</t>
@@ -3479,7 +3534,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr"/>
       <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Маржинальность оплаты</t>
@@ -3490,59 +3545,59 @@
           <t>финансы</t>
         </is>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="13">
         <f>IFERROR((D19-D20)/D19,"")</f>
         <v/>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="13">
         <f>IFERROR((E19-E20)/E19,"")</f>
         <v/>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="13">
         <f>IFERROR((G19-G20)/G19,"")</f>
         <v/>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="13">
         <f>IFERROR((H19-H20)/H19,"")</f>
         <v/>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="13">
         <f>IFERROR((J19-J20)/J19,"")</f>
         <v/>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="13">
         <f>IFERROR((K19-K20)/K19,"")</f>
         <v/>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="13">
         <f>IFERROR((M19-M20)/M19,"")</f>
         <v/>
       </c>
-      <c r="N22" s="12">
+      <c r="N22" s="13">
         <f>IFERROR((N19-N20)/N19,"")</f>
         <v/>
       </c>
-      <c r="P22" s="12">
+      <c r="P22" s="13">
         <f>IFERROR((P19-P20)/P19,"")</f>
         <v/>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="13">
         <f>IFERROR((Q19-Q20)/Q19,"")</f>
         <v/>
       </c>
-      <c r="S22" s="12">
+      <c r="S22" s="13">
         <f>IFERROR((S19-S20)/S19,"")</f>
         <v/>
       </c>
-      <c r="T22" s="12">
+      <c r="T22" s="13">
         <f>IFERROR((T19-T20)/T19,"")</f>
         <v/>
       </c>
-      <c r="V22" s="12">
+      <c r="V22" s="13">
         <f>IFERROR((V19-V20)/V19,"")</f>
         <v/>
       </c>
-      <c r="W22" s="12">
+      <c r="W22" s="13">
         <f>IFERROR((W19-W20)/W19,"")</f>
         <v/>
       </c>
@@ -3572,7 +3627,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3605,7 +3660,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>июл.26</t>
@@ -3765,201 +3822,201 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr"/>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Выручка всего</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>финансы</t>
         </is>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="17">
         <f>IFERROR('Платформа'!D10+'Поток-1'!D10,"")</f>
         <v/>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="17">
         <f>IFERROR('Платформа'!E10+'Поток-1'!E10,"")</f>
         <v/>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="18">
         <f>IFERROR(E4/E4,"")</f>
         <v/>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="17">
         <f>IFERROR('Платформа'!G10+'Поток-1'!G10,"")</f>
         <v/>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="17">
         <f>IFERROR('Платформа'!H10+'Поток-1'!H10,"")</f>
         <v/>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="18">
         <f>IFERROR(H4/H4,"")</f>
         <v/>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="17">
         <f>IFERROR('Платформа'!J10+'Поток-1'!J10,"")</f>
         <v/>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="17">
         <f>IFERROR('Платформа'!K10+'Поток-1'!K10,"")</f>
         <v/>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="18">
         <f>IFERROR(K4/K4,"")</f>
         <v/>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="17">
         <f>IFERROR('Платформа'!M10+'Поток-1'!M10,"")</f>
         <v/>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="17">
         <f>IFERROR('Платформа'!N10+'Поток-1'!N10,"")</f>
         <v/>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="18">
         <f>IFERROR(N4/N4,"")</f>
         <v/>
       </c>
-      <c r="P4" s="11">
+      <c r="P4" s="17">
         <f>IFERROR('Платформа'!P10+'Поток-1'!P10,"")</f>
         <v/>
       </c>
-      <c r="Q4" s="11">
+      <c r="Q4" s="17">
         <f>IFERROR('Платформа'!Q10+'Поток-1'!Q10,"")</f>
         <v/>
       </c>
-      <c r="R4" s="12">
+      <c r="R4" s="18">
         <f>IFERROR(Q4/Q4,"")</f>
         <v/>
       </c>
-      <c r="S4" s="11">
+      <c r="S4" s="17">
         <f>IFERROR('Платформа'!S10+'Поток-1'!S10,"")</f>
         <v/>
       </c>
-      <c r="T4" s="11">
+      <c r="T4" s="17">
         <f>IFERROR('Платформа'!T10+'Поток-1'!T10,"")</f>
         <v/>
       </c>
-      <c r="U4" s="12">
+      <c r="U4" s="18">
         <f>IFERROR(T4/T4,"")</f>
         <v/>
       </c>
-      <c r="V4" s="14">
+      <c r="V4" s="19">
         <f>IFERROR('Платформа'!V10+'Поток-1'!V10,"")</f>
         <v/>
       </c>
-      <c r="W4" s="14">
+      <c r="W4" s="19">
         <f>IFERROR('Платформа'!W10+'Поток-1'!W10,"")</f>
         <v/>
       </c>
-      <c r="X4" s="12">
+      <c r="X4" s="18">
         <f>IFERROR(W4/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr"/>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Расходы всего</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>финансы</t>
         </is>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="23">
         <f>IFERROR(SUM(D6:D12),"")</f>
         <v/>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="23">
         <f>IFERROR(SUM(E6:E12),"")</f>
         <v/>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="24">
         <f>IFERROR(E5/E4,"")</f>
         <v/>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="23">
         <f>IFERROR(SUM(G6:G12),"")</f>
         <v/>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="23">
         <f>IFERROR(SUM(H6:H12),"")</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="24">
         <f>IFERROR(H5/H4,"")</f>
         <v/>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="23">
         <f>IFERROR(SUM(J6:J12),"")</f>
         <v/>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="23">
         <f>IFERROR(SUM(K6:K12),"")</f>
         <v/>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="24">
         <f>IFERROR(K5/K4,"")</f>
         <v/>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="23">
         <f>IFERROR(SUM(M6:M12),"")</f>
         <v/>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="23">
         <f>IFERROR(SUM(N6:N12),"")</f>
         <v/>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="24">
         <f>IFERROR(N5/N4,"")</f>
         <v/>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="23">
         <f>IFERROR(SUM(P6:P12),"")</f>
         <v/>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="23">
         <f>IFERROR(SUM(Q6:Q12),"")</f>
         <v/>
       </c>
-      <c r="R5" s="12">
+      <c r="R5" s="24">
         <f>IFERROR(Q5/Q4,"")</f>
         <v/>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="23">
         <f>IFERROR(SUM(S6:S12),"")</f>
         <v/>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="23">
         <f>IFERROR(SUM(T6:T12),"")</f>
         <v/>
       </c>
-      <c r="U5" s="12">
+      <c r="U5" s="24">
         <f>IFERROR(T5/T4,"")</f>
         <v/>
       </c>
-      <c r="V5" s="14">
+      <c r="V5" s="25">
         <f>IFERROR(SUM(V6:V12),"")</f>
         <v/>
       </c>
-      <c r="W5" s="14">
+      <c r="W5" s="25">
         <f>IFERROR(SUM(W6:W12),"")</f>
         <v/>
       </c>
-      <c r="X5" s="12">
+      <c r="X5" s="26">
         <f>IFERROR(W5/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>М П1</t>
         </is>
@@ -3982,7 +4039,7 @@
         <f>IFERROR('Платформа'!E12+'Поток-1'!E12,"")</f>
         <v/>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <f>IFERROR(E6/E4,"")</f>
         <v/>
       </c>
@@ -3994,7 +4051,7 @@
         <f>IFERROR('Платформа'!H12+'Поток-1'!H12,"")</f>
         <v/>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="13">
         <f>IFERROR(H6/H4,"")</f>
         <v/>
       </c>
@@ -4006,7 +4063,7 @@
         <f>IFERROR('Платформа'!K12+'Поток-1'!K12,"")</f>
         <v/>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="13">
         <f>IFERROR(K6/K4,"")</f>
         <v/>
       </c>
@@ -4018,7 +4075,7 @@
         <f>IFERROR('Платформа'!N12+'Поток-1'!N12,"")</f>
         <v/>
       </c>
-      <c r="O6" s="12">
+      <c r="O6" s="13">
         <f>IFERROR(N6/N4,"")</f>
         <v/>
       </c>
@@ -4030,7 +4087,7 @@
         <f>IFERROR('Платформа'!Q12+'Поток-1'!Q12,"")</f>
         <v/>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="13">
         <f>IFERROR(Q6/Q4,"")</f>
         <v/>
       </c>
@@ -4042,7 +4099,7 @@
         <f>IFERROR('Платформа'!T12+'Поток-1'!T12,"")</f>
         <v/>
       </c>
-      <c r="U6" s="12">
+      <c r="U6" s="13">
         <f>IFERROR(T6/T4,"")</f>
         <v/>
       </c>
@@ -4054,25 +4111,25 @@
         <f>IFERROR('Платформа'!W12+'Поток-1'!W12,"")</f>
         <v/>
       </c>
-      <c r="X6" s="12">
+      <c r="X6" s="13">
         <f>IFERROR(W6/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>М</t>
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>П</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>ФОТ Маркетинг</t>
+          <t>ФОТ Платформа</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>маркетинг</t>
+          <t>операционка</t>
         </is>
       </c>
       <c r="D7" s="11">
@@ -4083,7 +4140,7 @@
         <f>IFERROR('Платформа'!E13,"")</f>
         <v/>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>IFERROR(E7/E4,"")</f>
         <v/>
       </c>
@@ -4095,7 +4152,7 @@
         <f>IFERROR('Платформа'!H13,"")</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <f>IFERROR(H7/H4,"")</f>
         <v/>
       </c>
@@ -4107,7 +4164,7 @@
         <f>IFERROR('Платформа'!K13,"")</f>
         <v/>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="13">
         <f>IFERROR(K7/K4,"")</f>
         <v/>
       </c>
@@ -4119,7 +4176,7 @@
         <f>IFERROR('Платформа'!N13,"")</f>
         <v/>
       </c>
-      <c r="O7" s="12">
+      <c r="O7" s="13">
         <f>IFERROR(N7/N4,"")</f>
         <v/>
       </c>
@@ -4131,7 +4188,7 @@
         <f>IFERROR('Платформа'!Q13,"")</f>
         <v/>
       </c>
-      <c r="R7" s="12">
+      <c r="R7" s="13">
         <f>IFERROR(Q7/Q4,"")</f>
         <v/>
       </c>
@@ -4143,7 +4200,7 @@
         <f>IFERROR('Платформа'!T13,"")</f>
         <v/>
       </c>
-      <c r="U7" s="12">
+      <c r="U7" s="13">
         <f>IFERROR(T7/T4,"")</f>
         <v/>
       </c>
@@ -4155,13 +4212,13 @@
         <f>IFERROR('Платформа'!W13,"")</f>
         <v/>
       </c>
-      <c r="X7" s="12">
+      <c r="X7" s="13">
         <f>IFERROR(W7/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>П1</t>
         </is>
@@ -4184,7 +4241,7 @@
         <f>IFERROR('Поток-1'!E13+'Поток-1'!E14,"")</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>IFERROR(E8/E4,"")</f>
         <v/>
       </c>
@@ -4196,7 +4253,7 @@
         <f>IFERROR('Поток-1'!H13+'Поток-1'!H14,"")</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <f>IFERROR(H8/H4,"")</f>
         <v/>
       </c>
@@ -4208,7 +4265,7 @@
         <f>IFERROR('Поток-1'!K13+'Поток-1'!K14,"")</f>
         <v/>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="13">
         <f>IFERROR(K8/K4,"")</f>
         <v/>
       </c>
@@ -4220,7 +4277,7 @@
         <f>IFERROR('Поток-1'!N13+'Поток-1'!N14,"")</f>
         <v/>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="13">
         <f>IFERROR(N8/N4,"")</f>
         <v/>
       </c>
@@ -4232,7 +4289,7 @@
         <f>IFERROR('Поток-1'!Q13+'Поток-1'!Q14,"")</f>
         <v/>
       </c>
-      <c r="R8" s="12">
+      <c r="R8" s="13">
         <f>IFERROR(Q8/Q4,"")</f>
         <v/>
       </c>
@@ -4244,7 +4301,7 @@
         <f>IFERROR('Поток-1'!T13+'Поток-1'!T14,"")</f>
         <v/>
       </c>
-      <c r="U8" s="12">
+      <c r="U8" s="13">
         <f>IFERROR(T8/T4,"")</f>
         <v/>
       </c>
@@ -4256,13 +4313,13 @@
         <f>IFERROR('Поток-1'!W13+'Поток-1'!W14,"")</f>
         <v/>
       </c>
-      <c r="X8" s="12">
+      <c r="X8" s="13">
         <f>IFERROR(W8/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>М П1</t>
         </is>
@@ -4285,7 +4342,7 @@
         <f>IFERROR('Платформа'!E14+'Поток-1'!E15,"")</f>
         <v/>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <f>IFERROR(E9/E4,"")</f>
         <v/>
       </c>
@@ -4297,7 +4354,7 @@
         <f>IFERROR('Платформа'!H14+'Поток-1'!H15,"")</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="13">
         <f>IFERROR(H9/H4,"")</f>
         <v/>
       </c>
@@ -4309,7 +4366,7 @@
         <f>IFERROR('Платформа'!K14+'Поток-1'!K15,"")</f>
         <v/>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="13">
         <f>IFERROR(K9/K4,"")</f>
         <v/>
       </c>
@@ -4321,7 +4378,7 @@
         <f>IFERROR('Платформа'!N14+'Поток-1'!N15,"")</f>
         <v/>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="13">
         <f>IFERROR(N9/N4,"")</f>
         <v/>
       </c>
@@ -4333,7 +4390,7 @@
         <f>IFERROR('Платформа'!Q14+'Поток-1'!Q15,"")</f>
         <v/>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="13">
         <f>IFERROR(Q9/Q4,"")</f>
         <v/>
       </c>
@@ -4345,7 +4402,7 @@
         <f>IFERROR('Платформа'!T14+'Поток-1'!T15,"")</f>
         <v/>
       </c>
-      <c r="U9" s="12">
+      <c r="U9" s="13">
         <f>IFERROR(T9/T4,"")</f>
         <v/>
       </c>
@@ -4357,13 +4414,13 @@
         <f>IFERROR('Платформа'!W14+'Поток-1'!W15,"")</f>
         <v/>
       </c>
-      <c r="X9" s="12">
+      <c r="X9" s="13">
         <f>IFERROR(W9/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>П</t>
         </is>
@@ -4386,7 +4443,7 @@
         <f>IFERROR('Платформа'!E15+'Платформа'!E16,"")</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>IFERROR(E10/E4,"")</f>
         <v/>
       </c>
@@ -4398,7 +4455,7 @@
         <f>IFERROR('Платформа'!H15+'Платформа'!H16,"")</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <f>IFERROR(H10/H4,"")</f>
         <v/>
       </c>
@@ -4410,7 +4467,7 @@
         <f>IFERROR('Платформа'!K15+'Платформа'!K16,"")</f>
         <v/>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="13">
         <f>IFERROR(K10/K4,"")</f>
         <v/>
       </c>
@@ -4422,7 +4479,7 @@
         <f>IFERROR('Платформа'!N15+'Платформа'!N16,"")</f>
         <v/>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="13">
         <f>IFERROR(N10/N4,"")</f>
         <v/>
       </c>
@@ -4434,7 +4491,7 @@
         <f>IFERROR('Платформа'!Q15+'Платформа'!Q16,"")</f>
         <v/>
       </c>
-      <c r="R10" s="12">
+      <c r="R10" s="13">
         <f>IFERROR(Q10/Q4,"")</f>
         <v/>
       </c>
@@ -4446,7 +4503,7 @@
         <f>IFERROR('Платформа'!T15+'Платформа'!T16,"")</f>
         <v/>
       </c>
-      <c r="U10" s="12">
+      <c r="U10" s="13">
         <f>IFERROR(T10/T4,"")</f>
         <v/>
       </c>
@@ -4458,13 +4515,13 @@
         <f>IFERROR('Платформа'!W15+'Платформа'!W16,"")</f>
         <v/>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="13">
         <f>IFERROR(W10/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -4487,7 +4544,7 @@
         <f>IFERROR('Платформа'!E17+'Поток-1'!E16,"")</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>IFERROR(E11/E4,"")</f>
         <v/>
       </c>
@@ -4499,7 +4556,7 @@
         <f>IFERROR('Платформа'!H17+'Поток-1'!H16,"")</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <f>IFERROR(H11/H4,"")</f>
         <v/>
       </c>
@@ -4511,7 +4568,7 @@
         <f>IFERROR('Платформа'!K17+'Поток-1'!K16,"")</f>
         <v/>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="13">
         <f>IFERROR(K11/K4,"")</f>
         <v/>
       </c>
@@ -4523,7 +4580,7 @@
         <f>IFERROR('Платформа'!N17+'Поток-1'!N16,"")</f>
         <v/>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="13">
         <f>IFERROR(N11/N4,"")</f>
         <v/>
       </c>
@@ -4535,7 +4592,7 @@
         <f>IFERROR('Платформа'!Q17+'Поток-1'!Q16,"")</f>
         <v/>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="13">
         <f>IFERROR(Q11/Q4,"")</f>
         <v/>
       </c>
@@ -4547,7 +4604,7 @@
         <f>IFERROR('Платформа'!T17+'Поток-1'!T16,"")</f>
         <v/>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="13">
         <f>IFERROR(T11/T4,"")</f>
         <v/>
       </c>
@@ -4559,13 +4616,13 @@
         <f>IFERROR('Платформа'!W17+'Поток-1'!W16,"")</f>
         <v/>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="13">
         <f>IFERROR(W11/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -4588,7 +4645,7 @@
         <f>IFERROR('Платформа'!E18+'Поток-1'!E17,"")</f>
         <v/>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>IFERROR(E12/E4,"")</f>
         <v/>
       </c>
@@ -4600,7 +4657,7 @@
         <f>IFERROR('Платформа'!H18+'Поток-1'!H17,"")</f>
         <v/>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <f>IFERROR(H12/H4,"")</f>
         <v/>
       </c>
@@ -4612,7 +4669,7 @@
         <f>IFERROR('Платформа'!K18+'Поток-1'!K17,"")</f>
         <v/>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="13">
         <f>IFERROR(K12/K4,"")</f>
         <v/>
       </c>
@@ -4624,7 +4681,7 @@
         <f>IFERROR('Платформа'!N18+'Поток-1'!N17,"")</f>
         <v/>
       </c>
-      <c r="O12" s="12">
+      <c r="O12" s="13">
         <f>IFERROR(N12/N4,"")</f>
         <v/>
       </c>
@@ -4636,7 +4693,7 @@
         <f>IFERROR('Платформа'!Q18+'Поток-1'!Q17,"")</f>
         <v/>
       </c>
-      <c r="R12" s="12">
+      <c r="R12" s="13">
         <f>IFERROR(Q12/Q4,"")</f>
         <v/>
       </c>
@@ -4648,7 +4705,7 @@
         <f>IFERROR('Платформа'!T18+'Поток-1'!T17,"")</f>
         <v/>
       </c>
-      <c r="U12" s="12">
+      <c r="U12" s="13">
         <f>IFERROR(T12/T4,"")</f>
         <v/>
       </c>
@@ -4660,104 +4717,104 @@
         <f>IFERROR('Платформа'!W18+'Поток-1'!W17,"")</f>
         <v/>
       </c>
-      <c r="X12" s="12">
+      <c r="X12" s="13">
         <f>IFERROR(W12/W4,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr"/>
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Маржинальная прибыль</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>финансы</t>
         </is>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="17">
         <f>IFERROR(D4-D5,"")</f>
         <v/>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="17">
         <f>IFERROR(E4-E5,"")</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="18">
         <f>IFERROR(E13/E4,"")</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="17">
         <f>IFERROR(G4-G5,"")</f>
         <v/>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="17">
         <f>IFERROR(H4-H5,"")</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="18">
         <f>IFERROR(H13/H4,"")</f>
         <v/>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="17">
         <f>IFERROR(J4-J5,"")</f>
         <v/>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="17">
         <f>IFERROR(K4-K5,"")</f>
         <v/>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="18">
         <f>IFERROR(K13/K4,"")</f>
         <v/>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="17">
         <f>IFERROR(M4-M5,"")</f>
         <v/>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="17">
         <f>IFERROR(N4-N5,"")</f>
         <v/>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="18">
         <f>IFERROR(N13/N4,"")</f>
         <v/>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="17">
         <f>IFERROR(P4-P5,"")</f>
         <v/>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="17">
         <f>IFERROR(Q4-Q5,"")</f>
         <v/>
       </c>
-      <c r="R13" s="12">
+      <c r="R13" s="18">
         <f>IFERROR(Q13/Q4,"")</f>
         <v/>
       </c>
-      <c r="S13" s="11">
+      <c r="S13" s="17">
         <f>IFERROR(S4-S5,"")</f>
         <v/>
       </c>
-      <c r="T13" s="11">
+      <c r="T13" s="17">
         <f>IFERROR(T4-T5,"")</f>
         <v/>
       </c>
-      <c r="U13" s="12">
+      <c r="U13" s="18">
         <f>IFERROR(T13/T4,"")</f>
         <v/>
       </c>
-      <c r="V13" s="14">
+      <c r="V13" s="19">
         <f>IFERROR(V4-V5,"")</f>
         <v/>
       </c>
-      <c r="W13" s="14">
+      <c r="W13" s="19">
         <f>IFERROR(W4-W5,"")</f>
         <v/>
       </c>
-      <c r="X13" s="12">
+      <c r="X13" s="18">
         <f>IFERROR(W13/W4,"")</f>
         <v/>
       </c>
@@ -4783,123 +4840,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>D3-SPC-01 · P&amp;L MainExperts по потокам — структура присланного файла, наши продукты</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr"/>
+      <c r="A2" s="30" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>Структура повторяет присланный P&amp;L (розница: сайт/маркетплейсы/корпоративные/свод):</t>
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Цвета (как в оригинале): зелёный — Выручка всего / Маржинальная прибыль; красный — Расходы;</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>верхний блок — воронка, ниже — расходы (РБ, ФОТ, инструменты, себестоимость, эквайринг, админ.),</t>
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>серый — считается автоматически (не заполнять); белое — ввод основателя; жёлтый/синий — метка воронки.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>маржинальная прибыль, юнит-метрики; отдельный лист «Свод» собирает по потокам. Заменены каналы:</t>
-        </is>
-      </c>
+      <c r="A5" s="30" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • «Сайт» → «Платформа» (Поток-2, самообслуживание): воронка визиты→оплаты.</t>
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Структура повторяет присланный P&amp;L (розница). Каналы заменены: «Сайт» → «Платформа» (Поток-2);</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • «Корпоративные/личные продажи» → «Поток-1» (агентство, 2 менеджера):</t>
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>личные продажи → «Поток-1» (агентство, 2 менеджера: лиды→созвоны→оплаты→суммы); «Свод» по двум потокам.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    воронка лиды→созвоны→оплаты→суммы оплат.</t>
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>ФОТ Платформы — единая строка на всю команду платформы (разработка, маркетинг, владелец, Саша, Вадим).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • «Свод» — по двум потокам (Платформа + Поток-1).</t>
-        </is>
-      </c>
+      <c r="A9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr"/>
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Честно: объёмы/суммы — ввод основателя; эквайринг 10% (Робокасса, docs/06); пороги/цели не заданы.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Честно, без выдумывания: все объёмы и суммы — пустые жёлтые ячейки (ввод основателя).</t>
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>Формулы (конверсии, CAC, маржа, свод) считаются автоматически (IFERROR). План/Факт помесячно + Год.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Эквайринг = 10% выручки (Робокасса, docs/06). Прочие ставки/суммы вводит основатель.</t>
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Оговорка: чистую юнит-экономику потоков обычно не смешивают; «Свод» консолидирует по запросу основателя.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Пороги/цели не заданы. План и Факт — два столбца на каждый месяц (июл–дек 2026) + Год.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Формулы (конверсии, CAC, эквайринг, маржа, юнит, свод) считаются автоматически (IFERROR).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Оговорка (правило проекта): для чистой юнит-экономики метрики Потока-1 и Потока-2 не смешивают</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>(разные каналы/экономика). Здесь «Свод» консолидирует по запросу основателя (единый ₽-P&amp;L компании).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>Источники: docs/dms/documents/D3-SPC-01__pnl-model.md · docs/dms/04-registry.md · docs/06 · docs/01.</t>
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Источники: docs/dms/documents/D3-SPC-01__pnl-model.md · docs/06 · docs/01.</t>
         </is>
       </c>
     </row>
